--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35B49A0F-99DC-47CF-8396-9A33A0C8F53A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A864B194-3BCF-4199-82E8-535C8273DA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7892,7 +7892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B34B74B-930F-45E3-89E0-DE657E44D212}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A07F781A-22BB-49E3-A4CA-8DF606B2FBD1}">
   <dimension ref="B2:AF1564"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38187,7 +38187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5767C759-D515-466C-BDA0-BB20A29B8B34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16853538-B568-4F86-A64D-849EED40AA61}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A864B194-3BCF-4199-82E8-535C8273DA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAEA6BC1-527E-4CEF-B8BD-D5302DECA2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7892,7 +7892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A07F781A-22BB-49E3-A4CA-8DF606B2FBD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FE24BF-A0C8-42AB-AF54-CEFC877DE36D}">
   <dimension ref="B2:AF1564"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38187,7 +38187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16853538-B568-4F86-A64D-849EED40AA61}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C924DA3E-54C3-49A0-8DF2-C27B955BC5E6}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAEA6BC1-527E-4CEF-B8BD-D5302DECA2B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{30914FE6-33CE-40EA-9CC8-AEE3C15EFE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7892,7 +7892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7FE24BF-A0C8-42AB-AF54-CEFC877DE36D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B780D67-9BCA-4FFD-9ACA-D52C72E15966}">
   <dimension ref="B2:AF1564"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38187,7 +38187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C924DA3E-54C3-49A0-8DF2-C27B955BC5E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F07F2-8D3C-4838-9577-A79C375DB03A}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_IND_grids_kan/SuppXLS/Scen_Base_VS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30914FE6-33CE-40EA-9CC8-AEE3C15EFE60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C345329C-9991-45DD-9672-49A9B8A22C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7892,7 +7892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B780D67-9BCA-4FFD-9ACA-D52C72E15966}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1BE52F0-162D-4AD0-A4C4-1EEF77D035DA}">
   <dimension ref="B2:AF1564"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -38187,7 +38187,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D6F07F2-8D3C-4838-9577-A79C375DB03A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3498C9C3-2EAD-45FE-8668-CC187EED7E07}">
   <dimension ref="B9:L20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
